--- a/docs/oc-regiones/alimentos/los-rios.xlsx
+++ b/docs/oc-regiones/alimentos/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M326"/>
+  <dimension ref="A1:M327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>745.53</v>
+        <v>741.7</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1624.07</v>
+        <v>1615.73</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>756.33</v>
+        <v>748.79</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1564.61</v>
+        <v>1548.99</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>802.72</v>
+        <v>794.3200000000001</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3746.17</v>
+        <v>3706.94</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1065.19</v>
+        <v>1059.36</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3931.84</v>
+        <v>3888.04</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3874.02</v>
+        <v>3830.86</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2056.07</v>
+        <v>2033.16</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1373.69</v>
+        <v>1371.94</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4720.97</v>
+        <v>4772.32</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1780.4</v>
+        <v>1786.26</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1404.46</v>
+        <v>1409.08</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7037.43</v>
+        <v>7060.57</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1065.72</v>
+        <v>1069.23</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1127.5</v>
+        <v>1135.31</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2965.32</v>
+        <v>2979.13</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2054.59</v>
+        <v>2069.4</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5328.89</v>
+        <v>5367.31</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1345.58</v>
+        <v>1355.28</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4768.72</v>
+        <v>4803.1</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>978.28</v>
+        <v>985.33</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>745.88</v>
+        <v>751.26</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7443.2</v>
+        <v>7496.86</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>746.26</v>
+        <v>751.64</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1583.85</v>
+        <v>1581.04</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1902.06</v>
+        <v>1898.68</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>847.5599999999999</v>
+        <v>846.0599999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1020.2</v>
+        <v>1018.39</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1443.07</v>
+        <v>1440.51</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1245.27</v>
+        <v>1243.07</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4800.02</v>
+        <v>4780.24</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>764.45</v>
+        <v>761.3</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6477.9</v>
+        <v>6451.2</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2636.57</v>
+        <v>2625.7</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1297.86</v>
+        <v>1295.84</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>802.62</v>
+        <v>806.76</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>870.14</v>
+        <v>876.28</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1411.91</v>
+        <v>1421.87</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>932.25</v>
+        <v>938.83</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>759.6799999999999</v>
+        <v>765.04</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1115.87</v>
+        <v>1123.75</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>6473.96</v>
+        <v>6391.73</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4403.22</v>
+        <v>4347.29</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2700.41</v>
+        <v>2666.11</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>864.03</v>
+        <v>862.16</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>11486.02</v>
+        <v>11461.16</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>820.28</v>
+        <v>816.84</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2260.16</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3169.16</v>
+        <v>3132.48</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>759.83</v>
+        <v>759.22</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>762.01</v>
+        <v>761.4</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1444.2</v>
+        <v>1443.04</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2346.98</v>
+        <v>2345.09</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>888.29</v>
+        <v>892.3200000000001</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>19250.94</v>
+        <v>19223.94</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>759.71</v>
+        <v>767.85</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1040.46</v>
+        <v>1053.83</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5144.64</v>
+        <v>5013.27</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>6640.56</v>
+        <v>6470.99</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3189.02</v>
+        <v>3107.59</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3609.11</v>
+        <v>3516.94</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6869.17</v>
+        <v>6693.76</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3385.57</v>
+        <v>3319.54</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>792.34</v>
+        <v>782.28</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5636.75</v>
+        <v>5565.2</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2359.09</v>
+        <v>2329.15</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>800.15</v>
+        <v>789.99</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2469.51</v>
+        <v>2433.93</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>901.54</v>
+        <v>888.55</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>961.58</v>
+        <v>949.15</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1098.01</v>
+        <v>1083.82</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>897.75</v>
+        <v>895.98</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1298.42</v>
+        <v>1298.43</v>
       </c>
     </row>
     <row r="77">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2720.85</v>
+        <v>2711.51</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3248.36</v>
+        <v>3237.21</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>799.34</v>
+        <v>796.59</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5775.07</v>
+        <v>5755.25</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5692.64</v>
+        <v>5673.1</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>829.53</v>
+        <v>825.15</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>870.26</v>
+        <v>864.8099999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>806</v>
+        <v>800.95</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>819.6</v>
+        <v>814.46</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>807.72</v>
+        <v>802.66</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>799.22</v>
+        <v>794.21</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3800.15</v>
+        <v>3825.05</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>25375.98</v>
+        <v>25717.71</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1391.46</v>
+        <v>1410.19</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1338.1</v>
+        <v>1358.47</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7048.02</v>
+        <v>7155.32</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3361.59</v>
+        <v>3412.77</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>899.65</v>
+        <v>921.53</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>879.9</v>
+        <v>901.3</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4145.19</v>
+        <v>4270.89</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3374.84</v>
+        <v>3475.15</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1965.54</v>
+        <v>2023.96</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>810.38</v>
+        <v>807.49</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>867.73</v>
+        <v>864.64</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5207.07</v>
+        <v>5188.53</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4543.5</v>
+        <v>4527.32</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>7795.74</v>
+        <v>7737.4</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1104.03</v>
+        <v>1095.77</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5746.47</v>
+        <v>5763.11</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5679.68</v>
+        <v>5709.02</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1331.48</v>
+        <v>1338.36</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>7674.5</v>
+        <v>7744.3</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1446.9</v>
+        <v>1460.06</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3463.44</v>
+        <v>3494.95</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1245.91</v>
+        <v>1254.58</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3793.32</v>
+        <v>3819.73</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2343.8</v>
+        <v>2360.11</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>8226.65</v>
+        <v>8280.83</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1333.3</v>
+        <v>1342.08</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2039.18</v>
+        <v>2052.61</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1501.37</v>
+        <v>1498.8</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>823.52</v>
+        <v>822.11</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1597.67</v>
+        <v>1596.02</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2879.57</v>
+        <v>2876.6</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2166.84</v>
+        <v>2164.6</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>808.5599999999999</v>
+        <v>807.72</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1517.36</v>
+        <v>1506.49</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2366.53</v>
+        <v>2349.58</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>6191.67</v>
+        <v>6157.95</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>975.24</v>
+        <v>969.9299999999999</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3366.69</v>
+        <v>3346.85</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>825.04</v>
+        <v>820.03</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1351.84</v>
+        <v>1353.14</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1066.72</v>
+        <v>1113.83</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>770.28</v>
+        <v>792.66</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>869.86</v>
+        <v>873.29</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1457.71</v>
+        <v>1463.46</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3649.91</v>
+        <v>3658.89</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2369.43</v>
+        <v>2375.26</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2899.95</v>
+        <v>2907.09</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1540.57</v>
+        <v>1544.36</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3170.56</v>
+        <v>3178.36</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1351.81</v>
+        <v>1355.13</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3641.43</v>
+        <v>3594.55</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>811.74</v>
+        <v>801.29</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>985.4</v>
+        <v>972.72</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>798.38</v>
+        <v>792.75</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1180.36</v>
+        <v>1198.85</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1173.06</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1133.24</v>
+        <v>1133.18</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1887.61</v>
+        <v>1887.52</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1580.92</v>
+        <v>1580.84</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1148.53</v>
+        <v>1143.4</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>807.6900000000001</v>
+        <v>804.08</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1097.96</v>
+        <v>1093.05</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>772.88</v>
+        <v>769.42</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>768.24</v>
+        <v>768.9</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2283.27</v>
+        <v>2292.7</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6774.42</v>
+        <v>6755.73</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2045.02</v>
+        <v>2039.38</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>6942.07</v>
+        <v>6861.93</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4195.83</v>
+        <v>4133.24</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>770.98</v>
+        <v>766.55</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>778.27</v>
+        <v>774.92</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2298.22</v>
+        <v>2264.97</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1677.53</v>
+        <v>1641.44</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>869.33</v>
+        <v>850.63</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>6625</v>
+        <v>6482.46</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1735.41</v>
+        <v>1695.03</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5145.13</v>
+        <v>5025.41</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>781.1900000000001</v>
+        <v>763.02</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4799.72</v>
+        <v>4646.67</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1369.88</v>
+        <v>1342.87</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>795.5</v>
+        <v>779.8099999999999</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1041.11</v>
+        <v>1013.7</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>783.99</v>
+        <v>763.35</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2358.58</v>
+        <v>2296.47</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>885.04</v>
+        <v>861.73</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>892.71</v>
+        <v>876.53</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>4210.94</v>
+        <v>4223.2</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3596.5</v>
+        <v>3606.97</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2873.46</v>
+        <v>2885.4</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1020.51</v>
+        <v>1024.75</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>833.0700000000001</v>
+        <v>840.14</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>849.64</v>
+        <v>848.22</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3339.84</v>
+        <v>3380.95</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>6421.69</v>
+        <v>6505.49</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>34824.83</v>
+        <v>35279.28</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3444.42</v>
+        <v>3529.18</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>3701.47</v>
+        <v>3792.56</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2583.16</v>
+        <v>2646.73</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>3818.89</v>
+        <v>3912.87</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>938.34</v>
+        <v>961.4400000000001</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1311.42</v>
+        <v>1343.7</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1492.68</v>
+        <v>1529.42</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1714.09</v>
+        <v>1756.28</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>780.87</v>
+        <v>795.64</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1084.54</v>
+        <v>1105.05</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>938.96</v>
+        <v>956.72</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1010.08</v>
+        <v>1021.57</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1814.6</v>
+        <v>1835.23</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>784.34</v>
+        <v>793.26</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>867.1</v>
+        <v>874.91</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>7055.24</v>
+        <v>7118.79</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>4306.39</v>
+        <v>4345.18</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2761.47</v>
+        <v>2786.35</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>6951.72</v>
+        <v>7014.34</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>5069.01</v>
+        <v>5114.68</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1237.67</v>
+        <v>1245.59</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1898.22</v>
+        <v>1910.36</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1256.44</v>
+        <v>1264.48</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1192.8</v>
+        <v>1196.55</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1364.71</v>
+        <v>1370.36</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>4338.74</v>
+        <v>4356.72</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>19143.63</v>
+        <v>19183.29</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2876.77</v>
+        <v>2864.41</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2074.78</v>
+        <v>2046.58</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1174.23</v>
+        <v>1164.21</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1997.09</v>
+        <v>1980.06</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1027.36</v>
+        <v>1038.85</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4556.47</v>
+        <v>4607.42</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2337.97</v>
+        <v>2355.68</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2910.34</v>
+        <v>2932.38</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1311.67</v>
+        <v>1305.92</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>795.39</v>
+        <v>791.9</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>4762.28</v>
+        <v>4710.47</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>4215.42</v>
+        <v>4169.56</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1114.24</v>
+        <v>1102.11</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1708.32</v>
+        <v>1704.45</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>6908.35</v>
+        <v>6892.67</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1373.83</v>
+        <v>1370.71</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>6450.35</v>
+        <v>6435.71</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>819.6799999999999</v>
+        <v>817.66</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>791.0700000000001</v>
+        <v>789.12</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1191.22</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>915.05</v>
+        <v>919.55</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1068.08</v>
+        <v>1073.33</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1604.27</v>
+        <v>1609.59</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1173.57</v>
+        <v>1177.47</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2288.85</v>
+        <v>2296.45</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>822.17</v>
+        <v>824.9</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>4405.89</v>
+        <v>4419.91</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>7680.98</v>
+        <v>7705.42</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>21496.98</v>
+        <v>21611.28</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2761.78</v>
+        <v>2801.3</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>968.86</v>
+        <v>982.72</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2838.82</v>
+        <v>2872.12</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2710.56</v>
+        <v>2742.36</v>
       </c>
     </row>
     <row r="246">
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5050.76</v>
+        <v>5110.01</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1426100-88-CM26</t>
+          <t>4230-73-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Carabineros de Chile - Prefectura Valdivia</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>CARNES NUBLE S A</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>96.518.070-2</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15514,13 +15514,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>846.59</v>
+        <v>2917.43</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>4230-73-CM26</t>
+          <t>1426100-88-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>CARNES NUBLE S A</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>96.518.070-2</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2883.6</v>
+        <v>856.52</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>804.87</v>
+        <v>814.3099999999999</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1768.16</v>
+        <v>1798.07</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1186.62</v>
+        <v>1206.69</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1534.5</v>
+        <v>1550.11</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>810.4299999999999</v>
+        <v>818.67</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>863.53</v>
+        <v>872.3099999999999</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>949.3</v>
+        <v>958.96</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>989.14</v>
+        <v>999.2</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3577.93</v>
+        <v>3614.32</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1642.26</v>
+        <v>1658.96</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>824.7</v>
+        <v>833.09</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2466.75</v>
+        <v>2489.88</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>4187.38</v>
+        <v>4226.66</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>2344.2</v>
+        <v>2366.19</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>6397.54</v>
+        <v>6457.54</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2071.96</v>
+        <v>2091.4</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1244.57</v>
+        <v>1235.13</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1660.54</v>
+        <v>1636.97</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1242</v>
+        <v>1224.93</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1009.34</v>
+        <v>1013.92</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>907.03</v>
+        <v>924.28</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>976.62</v>
+        <v>995.1799999999999</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>936.5599999999999</v>
+        <v>954.37</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1374.6</v>
+        <v>1400.73</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1277.42</v>
+        <v>1301.7</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>990.77</v>
+        <v>1009.61</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>7285.02</v>
+        <v>7449.31</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3761.16</v>
+        <v>3845.99</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>6372.73</v>
+        <v>6516.45</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>6910.74</v>
+        <v>7066.59</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>3941.99</v>
+        <v>4030.89</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>871.59</v>
+        <v>877.61</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2050.42</v>
+        <v>2064.58</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2994.92</v>
+        <v>3004.17</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1169.13</v>
+        <v>1172.74</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2642.24</v>
+        <v>2607.04</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>829.76</v>
+        <v>818.71</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>882.4</v>
+        <v>870.65</v>
       </c>
     </row>
     <row r="287">
@@ -17954,13 +17954,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1036.77</v>
+        <v>1022.96</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1426100-106-CM26</t>
+          <t>1426100-107-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18000,12 +18000,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>CARNES NUBLE S A</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.518.070-2</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
@@ -18015,13 +18015,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>825.59</v>
+        <v>2271.87</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1426100-105-CM26</t>
+          <t>1426100-106-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18061,12 +18061,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1658.3</v>
+        <v>814.59</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1426100-107-CM26</t>
+          <t>1426100-105-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18122,12 +18122,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>CARNES NUBLE S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>96.518.070-2</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2302.54</v>
+        <v>1636.21</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2371.08</v>
+        <v>2324.67</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>898.84</v>
+        <v>881.24</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>812.58</v>
+        <v>800.54</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>4773.69</v>
+        <v>4702.97</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>5562.48</v>
+        <v>5584.19</v>
       </c>
     </row>
     <row r="296">
@@ -18503,13 +18503,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1420.29</v>
+        <v>1434.58</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5740-234-CM26</t>
+          <t>5740-237-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18549,12 +18549,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>ALIPRES SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.634.476-3</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -18564,13 +18564,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2891.3</v>
+        <v>3240.12</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5740-237-CM26</t>
+          <t>5740-234-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18610,12 +18610,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>ALIPRES SPA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.634.476-3</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3227.56</v>
+        <v>2902.55</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>4591.77</v>
+        <v>4568.51</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>4247.4</v>
+        <v>4225.88</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>3350.64</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>4123.07</v>
+        <v>4102.18</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>17770.5</v>
+        <v>17680.48</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1288.01</v>
+        <v>1290.75</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3604.19</v>
+        <v>3611.87</v>
       </c>
     </row>
     <row r="306">
@@ -19113,13 +19113,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1563.83</v>
+        <v>1574.03</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1057548-738-CM26</t>
+          <t>1079694-216-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19144,12 +19144,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>SECCIÓN COMPRAS XIV ZONA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19159,12 +19159,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19174,13 +19174,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1840.87</v>
+        <v>787.01</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1079694-216-CM26</t>
+          <t>1057548-738-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19205,12 +19205,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19220,12 +19220,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>781.78</v>
+        <v>1853.19</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2780.83</v>
+        <v>2774.78</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2465.24</v>
+        <v>2459.87</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>6397.63</v>
+        <v>6383.71</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>1020.37</v>
+        <v>1018.15</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>798.78</v>
+        <v>797.04</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>34790.68</v>
+        <v>34589.31</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>2244.58</v>
+        <v>2231.58</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1462.1</v>
+        <v>1438.5</v>
       </c>
     </row>
     <row r="317">
@@ -19784,13 +19784,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1598.99</v>
+        <v>1573.19</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>952946-136-CM26</t>
+          <t>1057552-677-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19815,12 +19815,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.607.508-K</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19830,12 +19830,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>ANDREA ALEJANDRA MARTÍNEZ WESTERMEIER</t>
+          <t>Comercial e Industrial Cecinas La Unión Ltda.</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>15.261.043-2</t>
+          <t>76.115.539-3</t>
         </is>
       </c>
       <c r="K318" t="inlineStr"/>
@@ -19845,13 +19845,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>959.8099999999999</v>
+        <v>3510.32</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1057552-675-CM26</t>
+          <t>952946-136-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19871,17 +19871,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>61.607.508-K</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19891,12 +19891,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>ANDREA ALEJANDRA MARTÍNEZ WESTERMEIER</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>15.261.043-2</t>
         </is>
       </c>
       <c r="K319" t="inlineStr"/>
@@ -19906,13 +19906,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>780.77</v>
+        <v>944.42</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1057552-677-CM26</t>
+          <t>1057552-675-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -19952,12 +19952,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Comercial e Industrial Cecinas La Unión Ltda.</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>76.115.539-3</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K320" t="inlineStr"/>
@@ -19967,13 +19967,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>3567.52</v>
+        <v>768.25</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1057547-11305-CM26</t>
+          <t>952946-141-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -19998,12 +19998,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20013,12 +20013,12 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>COMERCIAL SURMIX SPA</t>
+          <t>ALIPRES SPA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.145.084-9</t>
+          <t>76.634.476-3</t>
         </is>
       </c>
       <c r="K321" t="inlineStr"/>
@@ -20028,13 +20028,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2364.85</v>
+        <v>1876.18</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>952946-141-CM26</t>
+          <t>1057547-11305-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20059,12 +20059,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20074,12 +20074,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>ALIPRES SPA</t>
+          <t>COMERCIAL SURMIX SPA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>76.634.476-3</t>
+          <t>77.145.084-9</t>
         </is>
       </c>
       <c r="K322" t="inlineStr"/>
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1886.63</v>
+        <v>2351.74</v>
       </c>
     </row>
     <row r="323">
@@ -20150,13 +20150,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>1181.48</v>
+        <v>1174.93</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>952946-144-CM26</t>
+          <t>952946-145-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -20196,12 +20196,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>ALIPRES SPA</t>
+          <t>COMERCIAL SURMIX SPA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>76.634.476-3</t>
+          <t>77.145.084-9</t>
         </is>
       </c>
       <c r="K324" t="inlineStr"/>
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>13274</v>
+        <v>1099.01</v>
       </c>
     </row>
     <row r="325">
@@ -20272,13 +20272,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2354.09</v>
+        <v>2342.52</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>952946-145-CM26</t>
+          <t>952946-144-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -20318,12 +20318,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>COMERCIAL SURMIX SPA</t>
+          <t>ALIPRES SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>77.145.084-9</t>
+          <t>76.634.476-3</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -20333,7 +20333,68 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1104.44</v>
+        <v>13208.74</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>1426100-149-CM26</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>ALIPRES SPA</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>76.634.476-3</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="n">
+        <v>5097.75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/alimentos/los-rios.xlsx
+++ b/docs/oc-regiones/alimentos/los-rios.xlsx
@@ -688,7 +688,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1920,7 +1924,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3034,7 +3042,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3717,7 +3729,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5555,7 +5571,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5616,7 +5636,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6470,7 +6494,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7027,7 +7055,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7580,7 +7612,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7706,7 +7742,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7893,7 +7933,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9072,7 +9116,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9881,7 +9929,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11312,7 +11364,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12186,7 +12242,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12430,7 +12490,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12552,7 +12616,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14345,7 +14413,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15333,7 +15405,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15951,7 +16027,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17195,7 +17275,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19447,7 +19531,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20012,7 +20100,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21443,7 +21535,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21691,7 +21787,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21939,7 +22039,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22130,7 +22234,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23878,7 +23986,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24695,7 +24807,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25577,7 +25693,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26569,7 +26689,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26817,7 +26941,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28610,7 +28738,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30858,7 +30990,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31927,7 +32063,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33110,7 +33250,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34358,7 +34502,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34923,7 +35071,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37549,7 +37701,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38789,7 +38945,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41167,7 +41327,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41289,7 +41453,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
